--- a/src/New-release-old/Contribution To OPH.xlsx
+++ b/src/New-release-old/Contribution To OPH.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\visualisations\dvc3200-3299\dvc3221-productivityflash\fig6\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://livemanchesterac-my.sharepoint.com/personal/nathan_mckeogh_manchester_ac_uk/Documents/Documents/GitHub Repos/TPI-quarterly-data-tool/src/New-release/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BF03C634-CE04-445A-8D7A-002E45B91C82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_5243AF8C0829B8832CD2F53CDADF57DB061F2031" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43D2C6F7-1CAE-41AA-B980-B61C878563EB}"/>
   <bookViews>
-    <workbookView xWindow="-26925" yWindow="-2670" windowWidth="21600" windowHeight="11235" xr2:uid="{DB6F8AE1-7616-4866-B5DD-A2A13535284F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="12" r:id="rId1"/>
+    <sheet name="Data for Dataviz" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -38,140 +38,122 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
-    <t>Figure 6: In 2024 the construction industry made the biggest upward contribution to output per hour in comparison with 2019</t>
-  </si>
-  <si>
-    <t>Contribution to growth of output per hour worked, percentage points, 2024 relative to 2019</t>
+    <t>Figure 6: In 2025Q1 the information and communication industry made the biggest upward contribution to output per hour in comparison with the 2019 average</t>
+  </si>
+  <si>
+    <t>Contribution to growth of output per hour worked, percentage points, 2025Q1 compared with 2019 average</t>
   </si>
   <si>
     <t>Notes</t>
   </si>
   <si>
-    <t>2. "Other services" industry includes: activities of households as employers, undifferentiated goods and services producing activities of households for own use, activities of membership organisations, repair of computers and personal and household goods and a variety of personal service activities not covered elsewhere in our Standard Industrial Classification (SIC) 2007</t>
-  </si>
-  <si>
-    <t>3. The relative size of an industry shown is based on the Current Price (CP) value from 2019</t>
-  </si>
-  <si>
-    <t>Unit</t>
-  </si>
-  <si>
-    <t>Percent and percentage points</t>
-  </si>
-  <si>
-    <t>Industry</t>
-  </si>
-  <si>
-    <t>Contribution</t>
-  </si>
-  <si>
-    <t>Relative size of industry</t>
-  </si>
-  <si>
-    <t>Whole Economy excluding imputed rental</t>
-  </si>
-  <si>
-    <t>Agriculture forestry and fishing</t>
-  </si>
-  <si>
-    <t>Mining and quarrying</t>
-  </si>
-  <si>
-    <t>Manufacturing</t>
-  </si>
-  <si>
-    <t>Electricity, gas, steam and air conditioning supply</t>
-  </si>
-  <si>
-    <t>Water supply; sewerage, waste management and remediation activities</t>
-  </si>
-  <si>
-    <t>Construction</t>
-  </si>
-  <si>
-    <t>Wholesale and retail trade; repair of motor vehicles and motorcycles</t>
-  </si>
-  <si>
-    <t>Transportation and storage</t>
-  </si>
-  <si>
-    <t>Accommodation and food service activities</t>
-  </si>
-  <si>
-    <t>Information and communication</t>
-  </si>
-  <si>
-    <t>Financial and insurance activities</t>
-  </si>
-  <si>
-    <t>Real estate activities excluding imputed rental</t>
-  </si>
-  <si>
-    <t>Professional, scientific and technical activities</t>
-  </si>
-  <si>
-    <t>Administrative and support service activities</t>
-  </si>
-  <si>
-    <t>Public administration and defence; compulsory social security</t>
-  </si>
-  <si>
-    <t>Education</t>
-  </si>
-  <si>
-    <t>Human health and social activities</t>
-  </si>
-  <si>
-    <t>Arts, entertainment and recreation</t>
-  </si>
-  <si>
-    <t>Other service activities including households as employers</t>
-  </si>
-  <si>
-    <t>Between-industry reallocation</t>
-  </si>
-  <si>
     <r>
-      <t>1.</t>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">1. </t>
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="10"/>
         <color rgb="FF323132"/>
-        <rFont val="Ari"/>
+        <rFont val="Arial"/>
       </rPr>
-      <t>    The industry contributions may not add up to the total growth in output per hour. This is due to the National Accounts balancing value and the impact of rounding.</t>
+      <t>The industry contributions may not add up to the total growth in output per hour. This is due to the National Accounts balancing value and the impact of rounding.</t>
     </r>
+  </si>
+  <si>
+    <t>2. "Other services" industry includes: activities of households as employers, undifferentiated goods and services producing activities of households for own use, activities of membership organisations, repair of computers and personal and household goods and a variety of personal service activities not covered elsewhere in our Standard Industrial Classification (SIC) 2007</t>
+  </si>
+  <si>
+    <t>3. The relative size of an industry shown is based on the Current Price (CP) value from 2019</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>Percent and percentage points</t>
+  </si>
+  <si>
+    <t>Industry</t>
+  </si>
+  <si>
+    <t>Contribution</t>
+  </si>
+  <si>
+    <t>Relative size of industry</t>
+  </si>
+  <si>
+    <t>Whole Economy excluding imputed rental</t>
+  </si>
+  <si>
+    <t>Information and communication</t>
+  </si>
+  <si>
+    <t>Construction</t>
+  </si>
+  <si>
+    <t>Manufacturing</t>
+  </si>
+  <si>
+    <t>Professional, scientific and technical activities</t>
+  </si>
+  <si>
+    <t>Administrative and support service activities</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>Agriculture, forestry and fishing</t>
+  </si>
+  <si>
+    <t>Wholesale and retail, trade; repair of motor vehicles and motor cycle</t>
+  </si>
+  <si>
+    <t>Transport and storage</t>
+  </si>
+  <si>
+    <t>Water supply; sewerage, waste management and remediation activities</t>
+  </si>
+  <si>
+    <t>Other service activities &amp; Activities of households as employers</t>
+  </si>
+  <si>
+    <t>Public administration and defence; compulsory social security</t>
+  </si>
+  <si>
+    <t>Arts, entertainment and recreation</t>
+  </si>
+  <si>
+    <t>Mining and quarrying</t>
+  </si>
+  <si>
+    <t>Electricity, gas, steam and air conditioning supply</t>
+  </si>
+  <si>
+    <t>Accommodation and food service activities</t>
+  </si>
+  <si>
+    <t>Financial and insurance activities</t>
+  </si>
+  <si>
+    <t>Real estate activities exluding imputed rental</t>
+  </si>
+  <si>
+    <t>Human health and social work activities</t>
+  </si>
+  <si>
+    <t>Inbetween Industry Allocation</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-  </numFmts>
-  <fonts count="7">
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -180,18 +162,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Ari"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="12"/>
-      <name val="Ari"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color rgb="FF323132"/>
-      <name val="Ari"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="2">
@@ -202,7 +185,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -210,39 +193,20 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="4">
-    <cellStyle name="Heading 1 2" xfId="2" xr:uid="{EC19BC3F-83CB-457B-BAEB-08FC1A5ADDC6}"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="3" xr:uid="{B828F6DE-1CCF-4BE7-A3A5-ED96AE5C16D8}"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -271,13 +235,13 @@
         <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="145F82"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="E87331"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="186C24"/>
       </a:accent3>
       <a:accent4>
         <a:srgbClr val="0F9ED5"/>
@@ -297,7 +261,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -563,321 +527,302 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6DA0522-E8CE-464E-88E1-C600CC410D98}">
-  <sheetPr>
-    <tabColor theme="9" tint="0.59999389629810485"/>
-  </sheetPr>
-  <dimension ref="A1:M33"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="13.1796875" style="4" customWidth="1"/>
-    <col min="2" max="2" width="14.81640625" style="4" customWidth="1"/>
-    <col min="3" max="4" width="8.7265625" style="4"/>
-    <col min="5" max="16384" width="8.7265625" style="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C33"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="1"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="1"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="1"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C7" s="1"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C8" s="1"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C9" s="1"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2">
+        <v>2.0100412500000001E-2</v>
+      </c>
+      <c r="C13" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2">
+        <v>1.253719803E-2</v>
+      </c>
+      <c r="C14" s="2">
+        <v>6.9003201E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2">
+        <v>1.195471501E-2</v>
+      </c>
+      <c r="C15" s="2">
+        <v>6.8623112999999999E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2">
+        <v>8.0452996199999998E-3</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0.10840704299999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="2">
+        <v>6.9445484199999992E-3</v>
+      </c>
+      <c r="C17" s="2">
+        <v>8.2918584000000004E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2">
+        <v>6.7201735500000007E-3</v>
+      </c>
+      <c r="C18" s="2">
+        <v>5.6846478999999998E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="2">
+        <v>2.6845154199999998E-3</v>
+      </c>
+      <c r="C19" s="2">
+        <v>6.3775208999999999E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="2">
+        <v>2.3882328399999998E-3</v>
+      </c>
+      <c r="C20" s="2">
+        <v>7.452246E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="2">
+        <v>1.6530713699999999E-3</v>
+      </c>
+      <c r="C21" s="2">
+        <v>0.112765633</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="2">
+        <v>1.2897184100000001E-3</v>
+      </c>
+      <c r="C22" s="2">
+        <v>4.4668243000000003E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="2">
+        <v>4.9809060000000001E-5</v>
+      </c>
+      <c r="C23" s="2">
+        <v>1.3556811E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="2">
+        <v>-2.575229E-5</v>
+      </c>
+      <c r="C24" s="2">
+        <v>2.1315774999999999E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="2">
+        <v>-1.5564455399999998E-3</v>
+      </c>
+      <c r="C25" s="2">
+        <v>5.4132358999999998E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="2">
+        <v>-1.6264905700000001E-3</v>
+      </c>
+      <c r="C26" s="2">
+        <v>1.6491039999999998E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="2">
+        <v>-1.7615811200000001E-3</v>
+      </c>
+      <c r="C27" s="2">
+        <v>1.1606726E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="2">
+        <v>-3.24909903E-3</v>
+      </c>
+      <c r="C28" s="2">
+        <v>1.6656535E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" s="2">
+        <v>-3.6436233600000002E-3</v>
+      </c>
+      <c r="C29" s="2">
+        <v>3.3096270999999997E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" s="2">
+        <v>-5.3982769600000001E-3</v>
+      </c>
+      <c r="C30" s="2">
+        <v>9.0201474000000004E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="2">
+        <v>-7.7027934300000003E-3</v>
+      </c>
+      <c r="C31" s="2">
+        <v>4.3743677000000002E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" s="2">
+        <v>-1.41555849E-2</v>
+      </c>
+      <c r="C32" s="2">
+        <v>8.4739581999999994E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="5"/>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="B5" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="5"/>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="B6" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="5"/>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="C7" s="5"/>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="C8" s="5"/>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="C9" s="5"/>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13" s="2">
-        <v>1.7543859649122688E-2</v>
-      </c>
-      <c r="C13" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B14" s="2">
-        <v>1.3715790875948744E-3</v>
-      </c>
-      <c r="C14" s="6">
-        <v>7.4522463759321518E-3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" s="2">
-        <v>-2.4307830860256872E-3</v>
-      </c>
-      <c r="C15" s="6">
-        <v>1.1606726164010102E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16" s="2">
-        <v>6.2975045744757862E-3</v>
-      </c>
-      <c r="C16" s="6">
-        <v>0.10840704303204758</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
-      <c r="A17" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" s="2">
-        <v>-2.4822608846388032E-3</v>
-      </c>
-      <c r="C17" s="6">
-        <v>1.6656534686127426E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
-      <c r="A18" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" s="2">
-        <v>-1.0735342421243923E-3</v>
-      </c>
-      <c r="C18" s="6">
-        <v>1.3556810621699061E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13">
-      <c r="A19" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B19" s="2">
-        <v>1.1125969648000281E-2</v>
-      </c>
-      <c r="C19" s="6">
-        <v>6.8623113493260487E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13">
-      <c r="A20" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B20" s="2">
-        <v>-1.5995125318988045E-3</v>
-      </c>
-      <c r="C20" s="6">
-        <v>0.11276563349886526</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13">
-      <c r="A21" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B21" s="2">
-        <v>1.0720378299835303E-3</v>
-      </c>
-      <c r="C21" s="6">
-        <v>4.4668242915980323E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13">
-      <c r="A22" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B22" s="2">
-        <v>-1.8239427758339033E-3</v>
-      </c>
-      <c r="C22" s="6">
-        <v>3.309627073240428E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13">
-      <c r="A23" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B23" s="2">
-        <v>1.0597489249332199E-2</v>
-      </c>
-      <c r="C23" s="6">
-        <v>6.9003200676102827E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13">
-      <c r="A24" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B24" s="2">
-        <v>-2.9304032094028239E-3</v>
-      </c>
-      <c r="C24" s="6">
-        <v>9.0201473789430595E-2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13">
-      <c r="A25" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B25" s="2">
-        <v>-7.163450933499101E-3</v>
-      </c>
-      <c r="C25" s="6">
-        <v>4.3743676706337692E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13">
-      <c r="A26" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B26" s="2">
-        <v>5.9686688452572183E-3</v>
-      </c>
-      <c r="C26" s="6">
-        <v>8.2918584111804111E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13">
-      <c r="A27" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B27" s="2">
-        <v>6.1728654371676021E-3</v>
-      </c>
-      <c r="C27" s="6">
-        <v>5.6846478980461641E-2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13">
-      <c r="A28" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B28" s="2">
-        <v>-1.792113137805279E-3</v>
-      </c>
-      <c r="C28" s="6">
-        <v>5.4132358603706431E-2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13">
-      <c r="A29" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B29" s="2">
-        <v>4.2561140553376746E-3</v>
-      </c>
-      <c r="C29" s="6">
-        <v>6.377520904795056E-2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13">
-      <c r="A30" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B30" s="2">
-        <v>-1.3088050678090787E-2</v>
-      </c>
-      <c r="C30" s="6">
-        <v>8.4739582356452264E-2</v>
-      </c>
-      <c r="D30" s="6"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
-      <c r="J30" s="3"/>
-      <c r="K30" s="3"/>
-      <c r="L30" s="3"/>
-      <c r="M30" s="3"/>
-    </row>
-    <row r="31" spans="1:13">
-      <c r="A31" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B31" s="2">
-        <v>-1.4732628984936685E-3</v>
-      </c>
-      <c r="C31" s="6">
-        <v>1.6491039541203328E-2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13">
-      <c r="A32" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B32" s="2">
-        <v>-1.002112814866548E-3</v>
-      </c>
-      <c r="C32" s="6">
-        <v>2.1315774666223874E-2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33" s="4" t="s">
-        <v>30</v>
-      </c>
       <c r="B33" s="2">
-        <v>7.5410581146533231E-3</v>
+        <v>4.9527779799999998E-3</v>
       </c>
     </row>
   </sheetData>
@@ -886,26 +831,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8a54c791-04d1-4dd7-97a3-a882d4048403">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="7c97fbf4-89e8-4607-8aa6-eba0d12e3a2a" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E0CEF6E26CBF2C4F8000DAAA032CD586" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4b00db03ba10acd9ce0de4b8508f462a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8a54c791-04d1-4dd7-97a3-a882d4048403" xmlns:ns3="7c97fbf4-89e8-4607-8aa6-eba0d12e3a2a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="93f033296de2705646020d6024e1f2eb" ns2:_="" ns3:_="">
     <xsd:import namespace="8a54c791-04d1-4dd7-97a3-a882d4048403"/>
@@ -1154,27 +1079,28 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94634A26-D175-489B-8FB0-BF01ED00B512}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="8a54c791-04d1-4dd7-97a3-a882d4048403"/>
-    <ds:schemaRef ds:uri="7c97fbf4-89e8-4607-8aa6-eba0d12e3a2a"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8a54c791-04d1-4dd7-97a3-a882d4048403">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="7c97fbf4-89e8-4607-8aa6-eba0d12e3a2a" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FBB8B66B-A9E5-442B-AD6B-11250A010C70}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3FDAB6B-AFAB-4EC6-B0E3-7D3ACEEEDD52}">
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{213D9663-DD5E-4730-B7BA-C70A77580769}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -1192,8 +1118,21 @@
 </ds:datastoreItem>
 </file>
 
-<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
-<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{078807bf-ce82-4688-bce0-0d811684dc46}" enabled="0" method="" siteId="{078807bf-ce82-4688-bce0-0d811684dc46}" removed="1"/>
-</clbl:labelList>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EDAD2DC3-87EC-4167-B2AD-C5DBB7ECB4E8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="8a54c791-04d1-4dd7-97a3-a882d4048403"/>
+    <ds:schemaRef ds:uri="7c97fbf4-89e8-4607-8aa6-eba0d12e3a2a"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8557CAEA-ABFE-4BAB-A82C-A482A20DAFD5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>